--- a/src_files_to_silver_validation.xlsx
+++ b/src_files_to_silver_validation.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\uthej\Downloads\PEI_assessment\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB71CA0E-D03F-48B1-B7F1-7EB7DEDA7F57}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EB84247-B12F-4426-B7EA-C01F938A5097}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="2" xr2:uid="{BF88EDFC-CE2B-40C6-8F71-DF8E3BFC082E}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" firstSheet="4" activeTab="10" xr2:uid="{BF88EDFC-CE2B-40C6-8F71-DF8E3BFC082E}"/>
   </bookViews>
   <sheets>
     <sheet name="sheet index - content" sheetId="20" r:id="rId1"/>
-    <sheet name="testplan  src_files--&gt;silver" sheetId="18" r:id="rId2"/>
-    <sheet name="required metadata mapping" sheetId="7" r:id="rId3"/>
+    <sheet name="required metadata mapping" sheetId="7" r:id="rId2"/>
+    <sheet name="testplan  src_files--&gt;silver" sheetId="18" r:id="rId3"/>
     <sheet name="testcases - src_files vs silver" sheetId="6" r:id="rId4"/>
     <sheet name="bug report" sheetId="9" r:id="rId5"/>
     <sheet name="metrics-summary" sheetId="19" r:id="rId6"/>
@@ -53,7 +53,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11723" uniqueCount="1728">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="11724" uniqueCount="1730">
   <si>
     <t>Order_ID,Item,Amount,Customer_ID</t>
   </si>
@@ -19348,6 +19348,14 @@
   </si>
   <si>
     <t>Overall results of shipping testing</t>
+  </si>
+  <si>
+    <t>Shipping.json file should be present in below path in databricks
+"/Volumes/pei/src/raw_files"</t>
+  </si>
+  <si>
+    <t>Order.csv file should be present in below path in databricks
+"/Volumes/pei/src/raw_files"</t>
   </si>
 </sst>
 </file>
@@ -19489,7 +19497,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -19518,6 +19526,7 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="1" quotePrefix="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="7" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -19896,13 +19905,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>2</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>10886</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>24</xdr:col>
-      <xdr:colOff>110718</xdr:colOff>
+      <xdr:col>21</xdr:col>
+      <xdr:colOff>327365</xdr:colOff>
       <xdr:row>42</xdr:row>
-      <xdr:rowOff>130185</xdr:rowOff>
+      <xdr:rowOff>141071</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -19925,8 +19934,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1219200" y="365760"/>
-          <a:ext cx="14616427" cy="7445385"/>
+          <a:off x="1698171" y="381000"/>
+          <a:ext cx="14617747" cy="7532471"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -19943,8 +19952,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>309509</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>436509</xdr:colOff>
       <xdr:row>67</xdr:row>
       <xdr:rowOff>138647</xdr:rowOff>
     </xdr:to>
@@ -19987,8 +19996,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>126613</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>253613</xdr:colOff>
       <xdr:row>90</xdr:row>
       <xdr:rowOff>47198</xdr:rowOff>
     </xdr:to>
@@ -20031,8 +20040,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>470947</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>597947</xdr:colOff>
       <xdr:row>103</xdr:row>
       <xdr:rowOff>174034</xdr:rowOff>
     </xdr:to>
@@ -20075,8 +20084,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>463326</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>590326</xdr:colOff>
       <xdr:row>127</xdr:row>
       <xdr:rowOff>19789</xdr:rowOff>
     </xdr:to>
@@ -20119,8 +20128,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>440464</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>567464</xdr:colOff>
       <xdr:row>149</xdr:row>
       <xdr:rowOff>31662</xdr:rowOff>
     </xdr:to>
@@ -20163,8 +20172,8 @@
       <xdr:rowOff>1</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>17</xdr:col>
-      <xdr:colOff>311728</xdr:colOff>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>401375</xdr:colOff>
       <xdr:row>151</xdr:row>
       <xdr:rowOff>71963</xdr:rowOff>
     </xdr:to>
@@ -20208,7 +20217,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>6</xdr:col>
-      <xdr:colOff>579663</xdr:colOff>
+      <xdr:colOff>94754</xdr:colOff>
       <xdr:row>192</xdr:row>
       <xdr:rowOff>157420</xdr:rowOff>
     </xdr:to>
@@ -20251,8 +20260,8 @@
       <xdr:rowOff>115455</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>20</xdr:col>
-      <xdr:colOff>127142</xdr:colOff>
+      <xdr:col>17</xdr:col>
+      <xdr:colOff>343789</xdr:colOff>
       <xdr:row>226</xdr:row>
       <xdr:rowOff>12956</xdr:rowOff>
     </xdr:to>
@@ -20296,7 +20305,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>29</xdr:col>
-      <xdr:colOff>176979</xdr:colOff>
+      <xdr:colOff>176978</xdr:colOff>
       <xdr:row>195</xdr:row>
       <xdr:rowOff>54230</xdr:rowOff>
     </xdr:to>
@@ -20336,13 +20345,13 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>233</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>10886</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>548857</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>669065</xdr:colOff>
       <xdr:row>258</xdr:row>
-      <xdr:rowOff>38042</xdr:rowOff>
+      <xdr:rowOff>48928</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -20365,8 +20374,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1697182" y="43041455"/>
-          <a:ext cx="7834039" cy="4656223"/>
+          <a:off x="1698171" y="43129200"/>
+          <a:ext cx="7803691" cy="4664471"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -20383,8 +20392,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>655546</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>775754</xdr:colOff>
       <xdr:row>288</xdr:row>
       <xdr:rowOff>39873</xdr:rowOff>
     </xdr:to>
@@ -20427,8 +20436,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>464178</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>591178</xdr:colOff>
       <xdr:row>322</xdr:row>
       <xdr:rowOff>123700</xdr:rowOff>
     </xdr:to>
@@ -20471,8 +20480,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>13</xdr:col>
-      <xdr:colOff>45893</xdr:colOff>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>172893</xdr:colOff>
       <xdr:row>355</xdr:row>
       <xdr:rowOff>146562</xdr:rowOff>
     </xdr:to>
@@ -20515,10 +20524,10 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>118993</xdr:colOff>
-      <xdr:row>388</xdr:row>
-      <xdr:rowOff>177340</xdr:rowOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>245993</xdr:colOff>
+      <xdr:row>389</xdr:row>
+      <xdr:rowOff>448</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -20560,7 +20569,7 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>517523</xdr:colOff>
+      <xdr:colOff>32614</xdr:colOff>
       <xdr:row>421</xdr:row>
       <xdr:rowOff>24926</xdr:rowOff>
     </xdr:to>
@@ -20603,8 +20612,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>438208</xdr:colOff>
+      <xdr:col>7</xdr:col>
+      <xdr:colOff>565208</xdr:colOff>
       <xdr:row>440</xdr:row>
       <xdr:rowOff>50566</xdr:rowOff>
     </xdr:to>
@@ -20647,8 +20656,8 @@
       <xdr:rowOff>173182</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>257733</xdr:colOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>384733</xdr:colOff>
       <xdr:row>472</xdr:row>
       <xdr:rowOff>13086</xdr:rowOff>
     </xdr:to>
@@ -20691,8 +20700,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>9</xdr:col>
-      <xdr:colOff>85402</xdr:colOff>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>212402</xdr:colOff>
       <xdr:row>500</xdr:row>
       <xdr:rowOff>110291</xdr:rowOff>
     </xdr:to>
@@ -20735,8 +20744,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>211845</xdr:colOff>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>338845</xdr:colOff>
       <xdr:row>519</xdr:row>
       <xdr:rowOff>134394</xdr:rowOff>
     </xdr:to>
@@ -20779,8 +20788,8 @@
       <xdr:rowOff>0</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>210440</xdr:colOff>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>337440</xdr:colOff>
       <xdr:row>546</xdr:row>
       <xdr:rowOff>3601</xdr:rowOff>
     </xdr:to>
@@ -20823,8 +20832,8 @@
       <xdr:rowOff>150090</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>14</xdr:col>
-      <xdr:colOff>334818</xdr:colOff>
+      <xdr:col>13</xdr:col>
+      <xdr:colOff>368435</xdr:colOff>
       <xdr:row>563</xdr:row>
       <xdr:rowOff>25017</xdr:rowOff>
     </xdr:to>
@@ -21749,11 +21758,11 @@
       <xdr:col>2</xdr:col>
       <xdr:colOff>0</xdr:colOff>
       <xdr:row>781</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
+      <xdr:rowOff>120316</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>153933</xdr:colOff>
+      <xdr:colOff>30017</xdr:colOff>
       <xdr:row>801</xdr:row>
       <xdr:rowOff>44586</xdr:rowOff>
     </xdr:to>
@@ -21778,8 +21787,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1693333" y="141695714"/>
-          <a:ext cx="3734124" cy="3673158"/>
+          <a:off x="1704474" y="141070263"/>
+          <a:ext cx="3639490" cy="3533744"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -22629,6 +22638,50 @@
     </xdr:pic>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>728</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>559758</xdr:colOff>
+      <xdr:row>762</xdr:row>
+      <xdr:rowOff>100207</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="2" name="Picture 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{79F279FF-C8B6-6526-6D5B-1345A90008D3}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId19"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="1699846" y="136550400"/>
+          <a:ext cx="6538527" cy="6477561"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
 </xdr:wsDr>
 </file>
 
@@ -23159,14 +23212,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>1503</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -23732,9 +23785,10 @@
     <col min="1" max="1" width="15.88671875" style="1" customWidth="1"/>
     <col min="2" max="2" width="8.88671875" style="1"/>
     <col min="3" max="3" width="13.5546875" style="1" customWidth="1"/>
-    <col min="4" max="4" width="8.88671875" style="1"/>
+    <col min="4" max="4" width="16" style="1" customWidth="1"/>
     <col min="5" max="5" width="12.21875" style="1" customWidth="1"/>
-    <col min="6" max="13" width="8.88671875" style="1"/>
+    <col min="6" max="12" width="8.88671875" style="1"/>
+    <col min="13" max="13" width="25.109375" style="1" customWidth="1"/>
     <col min="14" max="14" width="16.77734375" style="1" customWidth="1"/>
     <col min="15" max="17" width="8.88671875" style="1"/>
     <col min="23" max="16384" width="8.88671875" style="1"/>
@@ -23864,111 +23918,111 @@
     <row r="106" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="19" t="s">
         <v>1456</v>
       </c>
-      <c r="D108" s="18"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="18"/>
-      <c r="H108" s="18"/>
-      <c r="I108" s="18"/>
-      <c r="J108" s="18"/>
-      <c r="K108" s="18"/>
-      <c r="L108" s="18"/>
-      <c r="M108" s="18"/>
-      <c r="N108" s="18"/>
-      <c r="O108" s="18"/>
+      <c r="D108" s="19"/>
+      <c r="E108" s="19"/>
+      <c r="F108" s="19"/>
+      <c r="G108" s="19"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="19"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="19"/>
+      <c r="M108" s="19"/>
+      <c r="N108" s="19"/>
+      <c r="O108" s="19"/>
     </row>
     <row r="109" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-      <c r="H109" s="18"/>
-      <c r="I109" s="18"/>
-      <c r="J109" s="18"/>
-      <c r="K109" s="18"/>
-      <c r="L109" s="18"/>
-      <c r="M109" s="18"/>
-      <c r="N109" s="18"/>
-      <c r="O109" s="18"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="19"/>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19"/>
+      <c r="H109" s="19"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19"/>
+      <c r="K109" s="19"/>
+      <c r="L109" s="19"/>
+      <c r="M109" s="19"/>
+      <c r="N109" s="19"/>
+      <c r="O109" s="19"/>
     </row>
     <row r="110" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
-      <c r="E110" s="18"/>
-      <c r="F110" s="18"/>
-      <c r="G110" s="18"/>
-      <c r="H110" s="18"/>
-      <c r="I110" s="18"/>
-      <c r="J110" s="18"/>
-      <c r="K110" s="18"/>
-      <c r="L110" s="18"/>
-      <c r="M110" s="18"/>
-      <c r="N110" s="18"/>
-      <c r="O110" s="18"/>
+      <c r="C110" s="19"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="19"/>
+      <c r="G110" s="19"/>
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="19"/>
+      <c r="M110" s="19"/>
+      <c r="N110" s="19"/>
+      <c r="O110" s="19"/>
     </row>
     <row r="111" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="18"/>
-      <c r="D111" s="18"/>
-      <c r="E111" s="18"/>
-      <c r="F111" s="18"/>
-      <c r="G111" s="18"/>
-      <c r="H111" s="18"/>
-      <c r="I111" s="18"/>
-      <c r="J111" s="18"/>
-      <c r="K111" s="18"/>
-      <c r="L111" s="18"/>
-      <c r="M111" s="18"/>
-      <c r="N111" s="18"/>
-      <c r="O111" s="18"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="19"/>
+      <c r="G111" s="19"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="19"/>
+      <c r="K111" s="19"/>
+      <c r="L111" s="19"/>
+      <c r="M111" s="19"/>
+      <c r="N111" s="19"/>
+      <c r="O111" s="19"/>
     </row>
     <row r="112" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="18"/>
-      <c r="D112" s="18"/>
-      <c r="E112" s="18"/>
-      <c r="F112" s="18"/>
-      <c r="G112" s="18"/>
-      <c r="H112" s="18"/>
-      <c r="I112" s="18"/>
-      <c r="J112" s="18"/>
-      <c r="K112" s="18"/>
-      <c r="L112" s="18"/>
-      <c r="M112" s="18"/>
-      <c r="N112" s="18"/>
-      <c r="O112" s="18"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="19"/>
+      <c r="G112" s="19"/>
+      <c r="H112" s="19"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="19"/>
+      <c r="M112" s="19"/>
+      <c r="N112" s="19"/>
+      <c r="O112" s="19"/>
     </row>
     <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="18"/>
-      <c r="D113" s="18"/>
-      <c r="E113" s="18"/>
-      <c r="F113" s="18"/>
-      <c r="G113" s="18"/>
-      <c r="H113" s="18"/>
-      <c r="I113" s="18"/>
-      <c r="J113" s="18"/>
-      <c r="K113" s="18"/>
-      <c r="L113" s="18"/>
-      <c r="M113" s="18"/>
-      <c r="N113" s="18"/>
-      <c r="O113" s="18"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="19"/>
+      <c r="G113" s="19"/>
+      <c r="H113" s="19"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="19"/>
+      <c r="K113" s="19"/>
+      <c r="L113" s="19"/>
+      <c r="M113" s="19"/>
+      <c r="N113" s="19"/>
+      <c r="O113" s="19"/>
     </row>
     <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="18"/>
-      <c r="J114" s="18"/>
-      <c r="K114" s="18"/>
-      <c r="L114" s="18"/>
-      <c r="M114" s="18"/>
-      <c r="N114" s="18"/>
-      <c r="O114" s="18"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="19"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="19"/>
+      <c r="M114" s="19"/>
+      <c r="N114" s="19"/>
+      <c r="O114" s="19"/>
     </row>
     <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -24926,27 +24980,27 @@
       <c r="V550" s="1"/>
     </row>
     <row r="551" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C551" s="19" t="s">
+      <c r="C551" s="20" t="s">
         <v>1498</v>
       </c>
-      <c r="D551" s="19"/>
-      <c r="E551" s="19"/>
-      <c r="F551" s="19"/>
-      <c r="G551" s="19"/>
-      <c r="K551" s="19" t="s">
+      <c r="D551" s="20"/>
+      <c r="E551" s="20"/>
+      <c r="F551" s="20"/>
+      <c r="G551" s="20"/>
+      <c r="K551" s="20" t="s">
         <v>1499</v>
       </c>
-      <c r="L551" s="19"/>
-      <c r="M551" s="19"/>
-      <c r="N551" s="19"/>
-      <c r="O551" s="19"/>
-      <c r="R551" s="19" t="s">
+      <c r="L551" s="20"/>
+      <c r="M551" s="20"/>
+      <c r="N551" s="20"/>
+      <c r="O551" s="20"/>
+      <c r="R551" s="20" t="s">
         <v>1500</v>
       </c>
-      <c r="S551" s="19"/>
-      <c r="T551" s="19"/>
-      <c r="U551" s="19"/>
-      <c r="V551" s="19"/>
+      <c r="S551" s="20"/>
+      <c r="T551" s="20"/>
+      <c r="U551" s="20"/>
+      <c r="V551" s="20"/>
     </row>
     <row r="552" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R552" s="1"/>
@@ -25090,7 +25144,7 @@
       <c r="V565" s="1"/>
     </row>
     <row r="566" spans="3:28" x14ac:dyDescent="0.3">
-      <c r="C566" s="1" t="s">
+      <c r="C566" s="7" t="s">
         <v>255</v>
       </c>
       <c r="D566" s="1" t="s">
@@ -25105,7 +25159,7 @@
       <c r="G566" s="1" t="s">
         <v>526</v>
       </c>
-      <c r="K566" s="1" t="s">
+      <c r="K566" s="7" t="s">
         <v>255</v>
       </c>
       <c r="L566" s="1" t="s">
@@ -38579,14 +38633,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>1504</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -39289,111 +39343,111 @@
     <row r="106" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="19" t="s">
         <v>1456</v>
       </c>
-      <c r="D108" s="18"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="18"/>
-      <c r="H108" s="18"/>
-      <c r="I108" s="18"/>
-      <c r="J108" s="18"/>
-      <c r="K108" s="18"/>
-      <c r="L108" s="18"/>
-      <c r="M108" s="18"/>
-      <c r="N108" s="18"/>
-      <c r="O108" s="18"/>
+      <c r="D108" s="19"/>
+      <c r="E108" s="19"/>
+      <c r="F108" s="19"/>
+      <c r="G108" s="19"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="19"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="19"/>
+      <c r="M108" s="19"/>
+      <c r="N108" s="19"/>
+      <c r="O108" s="19"/>
     </row>
     <row r="109" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-      <c r="H109" s="18"/>
-      <c r="I109" s="18"/>
-      <c r="J109" s="18"/>
-      <c r="K109" s="18"/>
-      <c r="L109" s="18"/>
-      <c r="M109" s="18"/>
-      <c r="N109" s="18"/>
-      <c r="O109" s="18"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="19"/>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19"/>
+      <c r="H109" s="19"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19"/>
+      <c r="K109" s="19"/>
+      <c r="L109" s="19"/>
+      <c r="M109" s="19"/>
+      <c r="N109" s="19"/>
+      <c r="O109" s="19"/>
     </row>
     <row r="110" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
-      <c r="E110" s="18"/>
-      <c r="F110" s="18"/>
-      <c r="G110" s="18"/>
-      <c r="H110" s="18"/>
-      <c r="I110" s="18"/>
-      <c r="J110" s="18"/>
-      <c r="K110" s="18"/>
-      <c r="L110" s="18"/>
-      <c r="M110" s="18"/>
-      <c r="N110" s="18"/>
-      <c r="O110" s="18"/>
+      <c r="C110" s="19"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="19"/>
+      <c r="G110" s="19"/>
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="19"/>
+      <c r="M110" s="19"/>
+      <c r="N110" s="19"/>
+      <c r="O110" s="19"/>
     </row>
     <row r="111" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="18"/>
-      <c r="D111" s="18"/>
-      <c r="E111" s="18"/>
-      <c r="F111" s="18"/>
-      <c r="G111" s="18"/>
-      <c r="H111" s="18"/>
-      <c r="I111" s="18"/>
-      <c r="J111" s="18"/>
-      <c r="K111" s="18"/>
-      <c r="L111" s="18"/>
-      <c r="M111" s="18"/>
-      <c r="N111" s="18"/>
-      <c r="O111" s="18"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="19"/>
+      <c r="G111" s="19"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="19"/>
+      <c r="K111" s="19"/>
+      <c r="L111" s="19"/>
+      <c r="M111" s="19"/>
+      <c r="N111" s="19"/>
+      <c r="O111" s="19"/>
     </row>
     <row r="112" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="18"/>
-      <c r="D112" s="18"/>
-      <c r="E112" s="18"/>
-      <c r="F112" s="18"/>
-      <c r="G112" s="18"/>
-      <c r="H112" s="18"/>
-      <c r="I112" s="18"/>
-      <c r="J112" s="18"/>
-      <c r="K112" s="18"/>
-      <c r="L112" s="18"/>
-      <c r="M112" s="18"/>
-      <c r="N112" s="18"/>
-      <c r="O112" s="18"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="19"/>
+      <c r="G112" s="19"/>
+      <c r="H112" s="19"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="19"/>
+      <c r="M112" s="19"/>
+      <c r="N112" s="19"/>
+      <c r="O112" s="19"/>
     </row>
     <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="18"/>
-      <c r="D113" s="18"/>
-      <c r="E113" s="18"/>
-      <c r="F113" s="18"/>
-      <c r="G113" s="18"/>
-      <c r="H113" s="18"/>
-      <c r="I113" s="18"/>
-      <c r="J113" s="18"/>
-      <c r="K113" s="18"/>
-      <c r="L113" s="18"/>
-      <c r="M113" s="18"/>
-      <c r="N113" s="18"/>
-      <c r="O113" s="18"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="19"/>
+      <c r="G113" s="19"/>
+      <c r="H113" s="19"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="19"/>
+      <c r="K113" s="19"/>
+      <c r="L113" s="19"/>
+      <c r="M113" s="19"/>
+      <c r="N113" s="19"/>
+      <c r="O113" s="19"/>
     </row>
     <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="18"/>
-      <c r="J114" s="18"/>
-      <c r="K114" s="18"/>
-      <c r="L114" s="18"/>
-      <c r="M114" s="18"/>
-      <c r="N114" s="18"/>
-      <c r="O114" s="18"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="19"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="19"/>
+      <c r="M114" s="19"/>
+      <c r="N114" s="19"/>
+      <c r="O114" s="19"/>
     </row>
     <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -40397,27 +40451,27 @@
       <c r="V508" s="1"/>
     </row>
     <row r="509" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C509" s="19" t="s">
+      <c r="C509" s="20" t="s">
         <v>1498</v>
       </c>
-      <c r="D509" s="19"/>
-      <c r="E509" s="19"/>
-      <c r="F509" s="19"/>
-      <c r="G509" s="19"/>
-      <c r="K509" s="19" t="s">
+      <c r="D509" s="20"/>
+      <c r="E509" s="20"/>
+      <c r="F509" s="20"/>
+      <c r="G509" s="20"/>
+      <c r="K509" s="20" t="s">
         <v>1499</v>
       </c>
-      <c r="L509" s="19"/>
-      <c r="M509" s="19"/>
-      <c r="N509" s="19"/>
-      <c r="O509" s="19"/>
-      <c r="R509" s="19" t="s">
+      <c r="L509" s="20"/>
+      <c r="M509" s="20"/>
+      <c r="N509" s="20"/>
+      <c r="O509" s="20"/>
+      <c r="R509" s="20" t="s">
         <v>1500</v>
       </c>
-      <c r="S509" s="19"/>
-      <c r="T509" s="19"/>
-      <c r="U509" s="19"/>
-      <c r="V509" s="19"/>
+      <c r="S509" s="20"/>
+      <c r="T509" s="20"/>
+      <c r="U509" s="20"/>
+      <c r="V509" s="20"/>
     </row>
     <row r="510" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R510" s="1"/>
@@ -40777,15 +40831,15 @@
       <c r="Z528" s="1" t="s">
         <v>1326</v>
       </c>
-      <c r="AB528" s="20" t="s">
+      <c r="AB528" s="21" t="s">
         <v>1561</v>
       </c>
-      <c r="AC528" s="20"/>
-      <c r="AD528" s="20"/>
-      <c r="AE528" s="20"/>
-      <c r="AF528" s="20"/>
-      <c r="AG528" s="20"/>
-      <c r="AH528" s="20"/>
+      <c r="AC528" s="21"/>
+      <c r="AD528" s="21"/>
+      <c r="AE528" s="21"/>
+      <c r="AF528" s="21"/>
+      <c r="AG528" s="21"/>
+      <c r="AH528" s="21"/>
     </row>
     <row r="529" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C529" s="1" t="s">
@@ -40834,13 +40888,13 @@
       <c r="Z529" s="1" t="s">
         <v>1552</v>
       </c>
-      <c r="AB529" s="20"/>
-      <c r="AC529" s="20"/>
-      <c r="AD529" s="20"/>
-      <c r="AE529" s="20"/>
-      <c r="AF529" s="20"/>
-      <c r="AG529" s="20"/>
-      <c r="AH529" s="20"/>
+      <c r="AB529" s="21"/>
+      <c r="AC529" s="21"/>
+      <c r="AD529" s="21"/>
+      <c r="AE529" s="21"/>
+      <c r="AF529" s="21"/>
+      <c r="AG529" s="21"/>
+      <c r="AH529" s="21"/>
     </row>
     <row r="530" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C530" s="1" t="s">
@@ -40889,13 +40943,13 @@
       <c r="Z530" s="1" t="s">
         <v>1553</v>
       </c>
-      <c r="AB530" s="20"/>
-      <c r="AC530" s="20"/>
-      <c r="AD530" s="20"/>
-      <c r="AE530" s="20"/>
-      <c r="AF530" s="20"/>
-      <c r="AG530" s="20"/>
-      <c r="AH530" s="20"/>
+      <c r="AB530" s="21"/>
+      <c r="AC530" s="21"/>
+      <c r="AD530" s="21"/>
+      <c r="AE530" s="21"/>
+      <c r="AF530" s="21"/>
+      <c r="AG530" s="21"/>
+      <c r="AH530" s="21"/>
     </row>
     <row r="531" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C531" s="1" t="s">
@@ -40944,13 +40998,13 @@
       <c r="Z531" s="1" t="s">
         <v>1554</v>
       </c>
-      <c r="AB531" s="20"/>
-      <c r="AC531" s="20"/>
-      <c r="AD531" s="20"/>
-      <c r="AE531" s="20"/>
-      <c r="AF531" s="20"/>
-      <c r="AG531" s="20"/>
-      <c r="AH531" s="20"/>
+      <c r="AB531" s="21"/>
+      <c r="AC531" s="21"/>
+      <c r="AD531" s="21"/>
+      <c r="AE531" s="21"/>
+      <c r="AF531" s="21"/>
+      <c r="AG531" s="21"/>
+      <c r="AH531" s="21"/>
     </row>
     <row r="532" spans="3:34" x14ac:dyDescent="0.3">
       <c r="C532" s="1" t="s">
@@ -51611,14 +51665,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" s="1" customFormat="1" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>1606</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="3" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="4" spans="1:8" s="1" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -52180,7 +52234,7 @@
 
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA854085-DFEA-43F4-8D3B-F2821FC8B348}">
-  <dimension ref="A1:AB706"/>
+  <dimension ref="A1:AB725"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="15.88671875" style="1" customWidth="1"/>
@@ -52320,111 +52374,111 @@
     <row r="106" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="107" spans="3:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="108" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C108" s="18" t="s">
+      <c r="C108" s="19" t="s">
         <v>1456</v>
       </c>
-      <c r="D108" s="18"/>
-      <c r="E108" s="18"/>
-      <c r="F108" s="18"/>
-      <c r="G108" s="18"/>
-      <c r="H108" s="18"/>
-      <c r="I108" s="18"/>
-      <c r="J108" s="18"/>
-      <c r="K108" s="18"/>
-      <c r="L108" s="18"/>
-      <c r="M108" s="18"/>
-      <c r="N108" s="18"/>
-      <c r="O108" s="18"/>
+      <c r="D108" s="19"/>
+      <c r="E108" s="19"/>
+      <c r="F108" s="19"/>
+      <c r="G108" s="19"/>
+      <c r="H108" s="19"/>
+      <c r="I108" s="19"/>
+      <c r="J108" s="19"/>
+      <c r="K108" s="19"/>
+      <c r="L108" s="19"/>
+      <c r="M108" s="19"/>
+      <c r="N108" s="19"/>
+      <c r="O108" s="19"/>
     </row>
     <row r="109" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C109" s="18"/>
-      <c r="D109" s="18"/>
-      <c r="E109" s="18"/>
-      <c r="F109" s="18"/>
-      <c r="G109" s="18"/>
-      <c r="H109" s="18"/>
-      <c r="I109" s="18"/>
-      <c r="J109" s="18"/>
-      <c r="K109" s="18"/>
-      <c r="L109" s="18"/>
-      <c r="M109" s="18"/>
-      <c r="N109" s="18"/>
-      <c r="O109" s="18"/>
+      <c r="C109" s="19"/>
+      <c r="D109" s="19"/>
+      <c r="E109" s="19"/>
+      <c r="F109" s="19"/>
+      <c r="G109" s="19"/>
+      <c r="H109" s="19"/>
+      <c r="I109" s="19"/>
+      <c r="J109" s="19"/>
+      <c r="K109" s="19"/>
+      <c r="L109" s="19"/>
+      <c r="M109" s="19"/>
+      <c r="N109" s="19"/>
+      <c r="O109" s="19"/>
     </row>
     <row r="110" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C110" s="18"/>
-      <c r="D110" s="18"/>
-      <c r="E110" s="18"/>
-      <c r="F110" s="18"/>
-      <c r="G110" s="18"/>
-      <c r="H110" s="18"/>
-      <c r="I110" s="18"/>
-      <c r="J110" s="18"/>
-      <c r="K110" s="18"/>
-      <c r="L110" s="18"/>
-      <c r="M110" s="18"/>
-      <c r="N110" s="18"/>
-      <c r="O110" s="18"/>
+      <c r="C110" s="19"/>
+      <c r="D110" s="19"/>
+      <c r="E110" s="19"/>
+      <c r="F110" s="19"/>
+      <c r="G110" s="19"/>
+      <c r="H110" s="19"/>
+      <c r="I110" s="19"/>
+      <c r="J110" s="19"/>
+      <c r="K110" s="19"/>
+      <c r="L110" s="19"/>
+      <c r="M110" s="19"/>
+      <c r="N110" s="19"/>
+      <c r="O110" s="19"/>
     </row>
     <row r="111" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C111" s="18"/>
-      <c r="D111" s="18"/>
-      <c r="E111" s="18"/>
-      <c r="F111" s="18"/>
-      <c r="G111" s="18"/>
-      <c r="H111" s="18"/>
-      <c r="I111" s="18"/>
-      <c r="J111" s="18"/>
-      <c r="K111" s="18"/>
-      <c r="L111" s="18"/>
-      <c r="M111" s="18"/>
-      <c r="N111" s="18"/>
-      <c r="O111" s="18"/>
+      <c r="C111" s="19"/>
+      <c r="D111" s="19"/>
+      <c r="E111" s="19"/>
+      <c r="F111" s="19"/>
+      <c r="G111" s="19"/>
+      <c r="H111" s="19"/>
+      <c r="I111" s="19"/>
+      <c r="J111" s="19"/>
+      <c r="K111" s="19"/>
+      <c r="L111" s="19"/>
+      <c r="M111" s="19"/>
+      <c r="N111" s="19"/>
+      <c r="O111" s="19"/>
     </row>
     <row r="112" spans="3:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C112" s="18"/>
-      <c r="D112" s="18"/>
-      <c r="E112" s="18"/>
-      <c r="F112" s="18"/>
-      <c r="G112" s="18"/>
-      <c r="H112" s="18"/>
-      <c r="I112" s="18"/>
-      <c r="J112" s="18"/>
-      <c r="K112" s="18"/>
-      <c r="L112" s="18"/>
-      <c r="M112" s="18"/>
-      <c r="N112" s="18"/>
-      <c r="O112" s="18"/>
+      <c r="C112" s="19"/>
+      <c r="D112" s="19"/>
+      <c r="E112" s="19"/>
+      <c r="F112" s="19"/>
+      <c r="G112" s="19"/>
+      <c r="H112" s="19"/>
+      <c r="I112" s="19"/>
+      <c r="J112" s="19"/>
+      <c r="K112" s="19"/>
+      <c r="L112" s="19"/>
+      <c r="M112" s="19"/>
+      <c r="N112" s="19"/>
+      <c r="O112" s="19"/>
     </row>
     <row r="113" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C113" s="18"/>
-      <c r="D113" s="18"/>
-      <c r="E113" s="18"/>
-      <c r="F113" s="18"/>
-      <c r="G113" s="18"/>
-      <c r="H113" s="18"/>
-      <c r="I113" s="18"/>
-      <c r="J113" s="18"/>
-      <c r="K113" s="18"/>
-      <c r="L113" s="18"/>
-      <c r="M113" s="18"/>
-      <c r="N113" s="18"/>
-      <c r="O113" s="18"/>
+      <c r="C113" s="19"/>
+      <c r="D113" s="19"/>
+      <c r="E113" s="19"/>
+      <c r="F113" s="19"/>
+      <c r="G113" s="19"/>
+      <c r="H113" s="19"/>
+      <c r="I113" s="19"/>
+      <c r="J113" s="19"/>
+      <c r="K113" s="19"/>
+      <c r="L113" s="19"/>
+      <c r="M113" s="19"/>
+      <c r="N113" s="19"/>
+      <c r="O113" s="19"/>
     </row>
     <row r="114" spans="1:15" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="C114" s="18"/>
-      <c r="D114" s="18"/>
-      <c r="E114" s="18"/>
-      <c r="F114" s="18"/>
-      <c r="G114" s="18"/>
-      <c r="H114" s="18"/>
-      <c r="I114" s="18"/>
-      <c r="J114" s="18"/>
-      <c r="K114" s="18"/>
-      <c r="L114" s="18"/>
-      <c r="M114" s="18"/>
-      <c r="N114" s="18"/>
-      <c r="O114" s="18"/>
+      <c r="C114" s="19"/>
+      <c r="D114" s="19"/>
+      <c r="E114" s="19"/>
+      <c r="F114" s="19"/>
+      <c r="G114" s="19"/>
+      <c r="H114" s="19"/>
+      <c r="I114" s="19"/>
+      <c r="J114" s="19"/>
+      <c r="K114" s="19"/>
+      <c r="L114" s="19"/>
+      <c r="M114" s="19"/>
+      <c r="N114" s="19"/>
+      <c r="O114" s="19"/>
     </row>
     <row r="115" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
     <row r="116" spans="1:15" customFormat="1" x14ac:dyDescent="0.3"/>
@@ -53947,27 +54001,27 @@
       <c r="V436" s="1"/>
     </row>
     <row r="437" spans="1:22" x14ac:dyDescent="0.3">
-      <c r="C437" s="19" t="s">
+      <c r="C437" s="20" t="s">
         <v>1498</v>
       </c>
-      <c r="D437" s="19"/>
-      <c r="E437" s="19"/>
-      <c r="F437" s="19"/>
-      <c r="G437" s="19"/>
-      <c r="K437" s="19" t="s">
+      <c r="D437" s="20"/>
+      <c r="E437" s="20"/>
+      <c r="F437" s="20"/>
+      <c r="G437" s="20"/>
+      <c r="K437" s="20" t="s">
         <v>1499</v>
       </c>
-      <c r="L437" s="19"/>
-      <c r="M437" s="19"/>
-      <c r="N437" s="19"/>
-      <c r="O437" s="19"/>
-      <c r="R437" s="19" t="s">
+      <c r="L437" s="20"/>
+      <c r="M437" s="20"/>
+      <c r="N437" s="20"/>
+      <c r="O437" s="20"/>
+      <c r="R437" s="20" t="s">
         <v>1500</v>
       </c>
-      <c r="S437" s="19"/>
-      <c r="T437" s="19"/>
-      <c r="U437" s="19"/>
-      <c r="V437" s="19"/>
+      <c r="S437" s="20"/>
+      <c r="T437" s="20"/>
+      <c r="U437" s="20"/>
+      <c r="V437" s="20"/>
     </row>
     <row r="438" spans="1:22" x14ac:dyDescent="0.3">
       <c r="R438" s="1"/>
@@ -62102,6 +62156,11 @@
     <row r="706" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A706" s="9" t="s">
         <v>1583</v>
+      </c>
+    </row>
+    <row r="725" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A725" s="9" t="s">
+        <v>1605</v>
       </c>
     </row>
   </sheetData>
@@ -62578,6 +62637,472 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C7BF98-702D-4C66-BB9F-3F0FFCF7104A}">
+  <dimension ref="A2:I31"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.44140625" style="1" customWidth="1"/>
+    <col min="4" max="4" width="13.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.21875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="7.88671875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="15.44140625" style="1" customWidth="1"/>
+    <col min="8" max="8" width="37" style="1" customWidth="1"/>
+    <col min="9" max="9" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="16384" width="8.88671875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A2" s="17" t="s">
+        <v>1340</v>
+      </c>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
+      <c r="D2" s="17"/>
+      <c r="E2" s="17"/>
+      <c r="F2" s="17"/>
+      <c r="G2" s="17"/>
+      <c r="H2" s="17"/>
+    </row>
+    <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="17"/>
+      <c r="B3" s="17"/>
+      <c r="C3" s="17"/>
+      <c r="D3" s="17"/>
+      <c r="E3" s="17"/>
+      <c r="F3" s="17"/>
+      <c r="G3" s="17"/>
+      <c r="H3" s="17"/>
+    </row>
+    <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="17"/>
+      <c r="B4" s="17"/>
+      <c r="C4" s="17"/>
+      <c r="D4" s="17"/>
+      <c r="E4" s="17"/>
+      <c r="F4" s="17"/>
+      <c r="G4" s="17"/>
+      <c r="H4" s="17"/>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A9" s="6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B9" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C9" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E9" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F9" s="6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G9" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H9" s="6" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I9" s="6" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A10" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B10" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C10" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D10" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F10" s="5"/>
+      <c r="G10" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H10" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I10" s="5" t="s">
+        <v>1309</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A11" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>520</v>
+      </c>
+      <c r="C11" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>1310</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F11" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G11" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H11" s="5"/>
+      <c r="I11" s="5" t="s">
+        <v>1312</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>521</v>
+      </c>
+      <c r="C12" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D12" s="5" t="s">
+        <v>1313</v>
+      </c>
+      <c r="E12" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F12" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G12" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H12" s="5"/>
+      <c r="I12" s="5" t="s">
+        <v>1314</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>522</v>
+      </c>
+      <c r="C13" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>1315</v>
+      </c>
+      <c r="E13" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F13" s="5"/>
+      <c r="G13" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H13" s="5"/>
+      <c r="I13" s="5" t="s">
+        <v>1317</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="s">
+        <v>1303</v>
+      </c>
+      <c r="B14" s="5" t="s">
+        <v>523</v>
+      </c>
+      <c r="C14" s="5" t="s">
+        <v>1304</v>
+      </c>
+      <c r="D14" s="5" t="s">
+        <v>1318</v>
+      </c>
+      <c r="E14" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F14" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G14" s="5" t="s">
+        <v>1316</v>
+      </c>
+      <c r="H14" s="5"/>
+      <c r="I14" s="5" t="s">
+        <v>1319</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A19" s="6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B19" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C19" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D19" s="6" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E19" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F19" s="6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G19" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H19" s="6" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I19" s="6" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B20" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C20" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>1322</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F20" s="5"/>
+      <c r="G20" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H20" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I20" s="5" t="s">
+        <v>1323</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B21" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D21" s="5" t="s">
+        <v>1324</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F21" s="5" t="s">
+        <v>426</v>
+      </c>
+      <c r="G21" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H21" s="5"/>
+      <c r="I21" s="5" t="s">
+        <v>1325</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B22" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C22" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>1326</v>
+      </c>
+      <c r="E22" s="5" t="s">
+        <v>1327</v>
+      </c>
+      <c r="F22" s="5" t="s">
+        <v>1339</v>
+      </c>
+      <c r="G22" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H22" s="5"/>
+      <c r="I22" s="5" t="s">
+        <v>1328</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="s">
+        <v>1320</v>
+      </c>
+      <c r="B23" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C23" s="5" t="s">
+        <v>1321</v>
+      </c>
+      <c r="D23" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F23" s="5"/>
+      <c r="G23" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H23" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I23" s="5" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A28" s="6" t="s">
+        <v>1294</v>
+      </c>
+      <c r="B28" s="6" t="s">
+        <v>1295</v>
+      </c>
+      <c r="C28" s="6" t="s">
+        <v>1296</v>
+      </c>
+      <c r="D28" s="6" t="s">
+        <v>1297</v>
+      </c>
+      <c r="E28" s="6" t="s">
+        <v>1298</v>
+      </c>
+      <c r="F28" s="6" t="s">
+        <v>1299</v>
+      </c>
+      <c r="G28" s="6" t="s">
+        <v>1300</v>
+      </c>
+      <c r="H28" s="6" t="s">
+        <v>1301</v>
+      </c>
+      <c r="I28" s="6" t="s">
+        <v>1302</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A29" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B29" s="5" t="s">
+        <v>1332</v>
+      </c>
+      <c r="C29" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D29" s="5" t="s">
+        <v>1334</v>
+      </c>
+      <c r="E29" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F29" s="5"/>
+      <c r="G29" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H29" s="5" t="s">
+        <v>1308</v>
+      </c>
+      <c r="I29" s="5" t="s">
+        <v>1335</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A30" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B30" s="5" t="s">
+        <v>1336</v>
+      </c>
+      <c r="C30" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D30" s="5" t="s">
+        <v>1337</v>
+      </c>
+      <c r="E30" s="5" t="s">
+        <v>1311</v>
+      </c>
+      <c r="F30" s="5" t="s">
+        <v>361</v>
+      </c>
+      <c r="G30" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H30" s="5"/>
+      <c r="I30" s="5" t="s">
+        <v>1338</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A31" s="5" t="s">
+        <v>1331</v>
+      </c>
+      <c r="B31" s="5" t="s">
+        <v>254</v>
+      </c>
+      <c r="C31" s="5" t="s">
+        <v>1333</v>
+      </c>
+      <c r="D31" s="5" t="s">
+        <v>1305</v>
+      </c>
+      <c r="E31" s="5" t="s">
+        <v>1306</v>
+      </c>
+      <c r="F31" s="5"/>
+      <c r="G31" s="5" t="s">
+        <v>1307</v>
+      </c>
+      <c r="H31" s="5" t="s">
+        <v>1329</v>
+      </c>
+      <c r="I31" s="5" t="s">
+        <v>1330</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A2:H4"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{328821EE-C0F4-4AC6-8269-1852CB12DF62}">
   <dimension ref="A1:B33"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
@@ -62852,472 +63377,6 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{63C7BF98-702D-4C66-BB9F-3F0FFCF7104A}">
-  <dimension ref="A2:I31"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="11.6640625" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="20.44140625" style="1" customWidth="1"/>
-    <col min="4" max="4" width="13.109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="8.88671875" style="1"/>
-    <col min="7" max="7" width="9.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="37" style="1" customWidth="1"/>
-    <col min="9" max="9" width="22.44140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="16384" width="8.88671875" style="1"/>
-  </cols>
-  <sheetData>
-    <row r="2" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="16" t="s">
-        <v>1340</v>
-      </c>
-      <c r="B2" s="16"/>
-      <c r="C2" s="16"/>
-      <c r="D2" s="16"/>
-      <c r="E2" s="16"/>
-      <c r="F2" s="16"/>
-      <c r="G2" s="16"/>
-      <c r="H2" s="16"/>
-    </row>
-    <row r="3" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="16"/>
-      <c r="B3" s="16"/>
-      <c r="C3" s="16"/>
-      <c r="D3" s="16"/>
-      <c r="E3" s="16"/>
-      <c r="F3" s="16"/>
-      <c r="G3" s="16"/>
-      <c r="H3" s="16"/>
-    </row>
-    <row r="4" spans="1:9" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="16"/>
-      <c r="B4" s="16"/>
-      <c r="C4" s="16"/>
-      <c r="D4" s="16"/>
-      <c r="E4" s="16"/>
-      <c r="F4" s="16"/>
-      <c r="G4" s="16"/>
-      <c r="H4" s="16"/>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A9" s="6" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B9" s="6" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C9" s="6" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E9" s="6" t="s">
-        <v>1298</v>
-      </c>
-      <c r="F9" s="6" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G9" s="6" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H9" s="6" t="s">
-        <v>1301</v>
-      </c>
-      <c r="I9" s="6" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A10" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B10" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C10" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D10" s="5" t="s">
-        <v>1305</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F10" s="5"/>
-      <c r="G10" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H10" s="5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="I10" s="5" t="s">
-        <v>1309</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A11" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>520</v>
-      </c>
-      <c r="C11" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D11" s="5" t="s">
-        <v>1310</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F11" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G11" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H11" s="5"/>
-      <c r="I11" s="5" t="s">
-        <v>1312</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A12" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B12" s="5" t="s">
-        <v>521</v>
-      </c>
-      <c r="C12" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D12" s="5" t="s">
-        <v>1313</v>
-      </c>
-      <c r="E12" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F12" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G12" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H12" s="5"/>
-      <c r="I12" s="5" t="s">
-        <v>1314</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A13" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>522</v>
-      </c>
-      <c r="C13" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>1315</v>
-      </c>
-      <c r="E13" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F13" s="5"/>
-      <c r="G13" s="5" t="s">
-        <v>1316</v>
-      </c>
-      <c r="H13" s="5"/>
-      <c r="I13" s="5" t="s">
-        <v>1317</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A14" s="5" t="s">
-        <v>1303</v>
-      </c>
-      <c r="B14" s="5" t="s">
-        <v>523</v>
-      </c>
-      <c r="C14" s="5" t="s">
-        <v>1304</v>
-      </c>
-      <c r="D14" s="5" t="s">
-        <v>1318</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F14" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G14" s="5" t="s">
-        <v>1316</v>
-      </c>
-      <c r="H14" s="5"/>
-      <c r="I14" s="5" t="s">
-        <v>1319</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A19" s="6" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B19" s="6" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C19" s="6" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E19" s="6" t="s">
-        <v>1298</v>
-      </c>
-      <c r="F19" s="6" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G19" s="6" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H19" s="6" t="s">
-        <v>1301</v>
-      </c>
-      <c r="I19" s="6" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B20" s="5" t="s">
-        <v>251</v>
-      </c>
-      <c r="C20" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>1322</v>
-      </c>
-      <c r="E20" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F20" s="5"/>
-      <c r="G20" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H20" s="5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="I20" s="5" t="s">
-        <v>1323</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A21" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>252</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D21" s="5" t="s">
-        <v>1324</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F21" s="5" t="s">
-        <v>426</v>
-      </c>
-      <c r="G21" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H21" s="5"/>
-      <c r="I21" s="5" t="s">
-        <v>1325</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>253</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D22" s="5" t="s">
-        <v>1326</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>1327</v>
-      </c>
-      <c r="F22" s="5" t="s">
-        <v>1339</v>
-      </c>
-      <c r="G22" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H22" s="5"/>
-      <c r="I22" s="5" t="s">
-        <v>1328</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="5" t="s">
-        <v>1320</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>1321</v>
-      </c>
-      <c r="D23" s="5" t="s">
-        <v>1305</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F23" s="5"/>
-      <c r="G23" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H23" s="5" t="s">
-        <v>1329</v>
-      </c>
-      <c r="I23" s="5" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A28" s="6" t="s">
-        <v>1294</v>
-      </c>
-      <c r="B28" s="6" t="s">
-        <v>1295</v>
-      </c>
-      <c r="C28" s="6" t="s">
-        <v>1296</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>1297</v>
-      </c>
-      <c r="E28" s="6" t="s">
-        <v>1298</v>
-      </c>
-      <c r="F28" s="6" t="s">
-        <v>1299</v>
-      </c>
-      <c r="G28" s="6" t="s">
-        <v>1300</v>
-      </c>
-      <c r="H28" s="6" t="s">
-        <v>1301</v>
-      </c>
-      <c r="I28" s="6" t="s">
-        <v>1302</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A29" s="5" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B29" s="5" t="s">
-        <v>1332</v>
-      </c>
-      <c r="C29" s="5" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D29" s="5" t="s">
-        <v>1334</v>
-      </c>
-      <c r="E29" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F29" s="5"/>
-      <c r="G29" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H29" s="5" t="s">
-        <v>1308</v>
-      </c>
-      <c r="I29" s="5" t="s">
-        <v>1335</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="5" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B30" s="5" t="s">
-        <v>1336</v>
-      </c>
-      <c r="C30" s="5" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D30" s="5" t="s">
-        <v>1337</v>
-      </c>
-      <c r="E30" s="5" t="s">
-        <v>1311</v>
-      </c>
-      <c r="F30" s="5" t="s">
-        <v>361</v>
-      </c>
-      <c r="G30" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H30" s="5"/>
-      <c r="I30" s="5" t="s">
-        <v>1338</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="5" t="s">
-        <v>1331</v>
-      </c>
-      <c r="B31" s="5" t="s">
-        <v>254</v>
-      </c>
-      <c r="C31" s="5" t="s">
-        <v>1333</v>
-      </c>
-      <c r="D31" s="5" t="s">
-        <v>1305</v>
-      </c>
-      <c r="E31" s="5" t="s">
-        <v>1306</v>
-      </c>
-      <c r="F31" s="5"/>
-      <c r="G31" s="5" t="s">
-        <v>1307</v>
-      </c>
-      <c r="H31" s="5" t="s">
-        <v>1329</v>
-      </c>
-      <c r="I31" s="5" t="s">
-        <v>1330</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A2:H4"/>
-  </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -63340,14 +63399,14 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="17" t="s">
+      <c r="A1" s="18" t="s">
         <v>1503</v>
       </c>
-      <c r="B1" s="17"/>
+      <c r="B1" s="18"/>
     </row>
     <row r="2" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
+      <c r="A2" s="18"/>
+      <c r="B2" s="18"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A5" s="6" t="s">
@@ -63775,7 +63834,7 @@
       <c r="C21" s="5" t="s">
         <v>1396</v>
       </c>
-      <c r="D21" s="5" t="s">
+      <c r="D21" s="8" t="s">
         <v>1477</v>
       </c>
       <c r="E21" s="5" t="s">
@@ -63896,14 +63955,14 @@
       </c>
     </row>
     <row r="29" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="17" t="s">
+      <c r="A29" s="18" t="s">
         <v>1504</v>
       </c>
-      <c r="B29" s="17"/>
+      <c r="B29" s="18"/>
     </row>
     <row r="30" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="17"/>
-      <c r="B30" s="17"/>
+      <c r="A30" s="18"/>
+      <c r="B30" s="18"/>
     </row>
     <row r="31" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="32" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
@@ -63945,7 +64004,7 @@
         <v>1374</v>
       </c>
       <c r="D35" s="8" t="s">
-        <v>1505</v>
+        <v>1729</v>
       </c>
       <c r="E35" s="5" t="s">
         <v>1320</v>
@@ -64455,17 +64514,19 @@
       </c>
     </row>
     <row r="55" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
-    <row r="56" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
+    <row r="56" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="G56" s="16"/>
+    </row>
     <row r="57" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3"/>
     <row r="58" spans="1:8" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="17" t="s">
+      <c r="A58" s="18" t="s">
         <v>1606</v>
       </c>
-      <c r="B58" s="17"/>
+      <c r="B58" s="18"/>
     </row>
     <row r="59" spans="1:8" x14ac:dyDescent="0.3">
-      <c r="A59" s="17"/>
-      <c r="B59" s="17"/>
+      <c r="A59" s="18"/>
+      <c r="B59" s="18"/>
     </row>
     <row r="62" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A62" s="6" t="s">
@@ -64504,7 +64565,7 @@
         <v>1374</v>
       </c>
       <c r="D63" s="8" t="s">
-        <v>1567</v>
+        <v>1728</v>
       </c>
       <c r="E63" s="5" t="s">
         <v>1331</v>
